--- a/artfynd/A 48926-2021 artfynd.xlsx
+++ b/artfynd/A 48926-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133900590</v>
       </c>
       <c r="B2" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>133900609</v>
       </c>
       <c r="B3" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48926-2021 artfynd.xlsx
+++ b/artfynd/A 48926-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133900590</v>
+        <v>133900603</v>
       </c>
       <c r="B2" t="n">
-        <v>106229</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607105</v>
+        <v>607068</v>
       </c>
       <c r="R2" t="n">
-        <v>6580207</v>
+        <v>6580222</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133900609</v>
+        <v>133900590</v>
       </c>
       <c r="B3" t="n">
-        <v>106229</v>
+        <v>106236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607093</v>
+        <v>607105</v>
       </c>
       <c r="R3" t="n">
-        <v>6580236</v>
+        <v>6580207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,814 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133900596</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>606714</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6579982</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133900609</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607093</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6580236</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133900573</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>606807</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6580105</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133900574</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>607047</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6580181</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133900587</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>606741</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6579991</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133900588</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>606726</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6579983</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133900610</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>607107</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6580212</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventeringar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133900604</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogartorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>607106</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6580211</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Härad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Camilla Ährlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Naturvärdesinventeringar</t>
         </is>

--- a/artfynd/A 48926-2021 artfynd.xlsx
+++ b/artfynd/A 48926-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900590</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900596</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900573</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900574</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900587</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900610</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,8 +1732,25 @@
           <t>Naturvärdesinventeringar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133900604</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>